--- a/tame_output/ON/bt/strategyON_20231225.xlsx
+++ b/tame_output/ON/bt/strategyON_20231225.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>501.5%</t>
+          <t>501.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-119.5%</t>
+          <t>-119.6%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-30.2%</t>
         </is>
       </c>
     </row>
@@ -43422,16 +43422,16 @@
         <v>3.121045839271831</v>
       </c>
       <c r="D1822" t="n">
-        <v>0.2289958085282446</v>
+        <v>0.2286498402049127</v>
       </c>
       <c r="E1822" t="n">
-        <v>3.212287738369382</v>
+        <v>3.21214935104005</v>
       </c>
       <c r="F1822" t="n">
-        <v>1.79145343605144</v>
+        <v>1.791106203734773</v>
       </c>
       <c r="G1822" t="n">
-        <v>4.195917900902697</v>
+        <v>4.195709561512697</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231225.xlsx
+++ b/tame_output/ON/bt/strategyON_20231225.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>501.4%</t>
+          <t>501.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-119.6%</t>
+          <t>-119.5%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-30.1%</t>
         </is>
       </c>
     </row>
@@ -43422,16 +43422,16 @@
         <v>3.121045839271831</v>
       </c>
       <c r="D1822" t="n">
-        <v>0.2286498402049127</v>
+        <v>0.2289977457812463</v>
       </c>
       <c r="E1822" t="n">
-        <v>3.21214935104005</v>
+        <v>3.212288513270583</v>
       </c>
       <c r="F1822" t="n">
-        <v>1.791106203734773</v>
+        <v>1.791455612359032</v>
       </c>
       <c r="G1822" t="n">
-        <v>4.195709561512697</v>
+        <v>4.195919206687252</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231225.xlsx
+++ b/tame_output/ON/bt/strategyON_20231225.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>501.5%</t>
+          <t>494.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-119.5%</t>
+          <t>-127.8%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-24.5%</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-38.3%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113.4%</t>
+          <t>111.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>106.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
     </row>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844648</v>
+        <v>3.118866618844647</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.123416866373824</v>
+        <v>3.123416866373823</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502552</v>
+        <v>3.141819250502551</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487813</v>
+        <v>3.146053372487812</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823384</v>
+        <v>3.146265744823383</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524824</v>
+        <v>3.157777201524823</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068704</v>
+        <v>3.157294380068703</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714846</v>
+        <v>3.147014107714845</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097102</v>
+        <v>3.163432091097101</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762262</v>
+        <v>3.169279212762261</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.18551435596348</v>
+        <v>3.185514355963479</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583695</v>
+        <v>3.199276732583694</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742725</v>
+        <v>3.238767863742724</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589525</v>
+        <v>3.260068416589524</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872958</v>
+        <v>3.306739876872957</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.31216459594633</v>
+        <v>3.312164595946329</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43048,7 +43048,7 @@
         <v>45268</v>
       </c>
       <c r="B1806" t="n">
-        <v>3.31844982914334</v>
+        <v>3.318449829143339</v>
       </c>
       <c r="C1806" t="n">
         <v>3.100133560631823</v>
@@ -43071,7 +43071,7 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308504</v>
+        <v>3.311781349308503</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
@@ -43094,7 +43094,7 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257517</v>
+        <v>3.271427670257516</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
@@ -43117,7 +43117,7 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.252962387441541</v>
+        <v>3.25296238744154</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
@@ -43140,7 +43140,7 @@
         <v>45272</v>
       </c>
       <c r="B1810" t="n">
-        <v>3.241257540662169</v>
+        <v>3.241257540662168</v>
       </c>
       <c r="C1810" t="n">
         <v>3.119070330776787</v>
@@ -43163,7 +43163,7 @@
         <v>45273</v>
       </c>
       <c r="B1811" t="n">
-        <v>3.285495323543325</v>
+        <v>3.285495323543324</v>
       </c>
       <c r="C1811" t="n">
         <v>3.132597942828719</v>
@@ -43186,7 +43186,7 @@
         <v>45274</v>
       </c>
       <c r="B1812" t="n">
-        <v>3.287726162978609</v>
+        <v>3.287726162978608</v>
       </c>
       <c r="C1812" t="n">
         <v>3.139185323079984</v>
@@ -43209,7 +43209,7 @@
         <v>45275</v>
       </c>
       <c r="B1813" t="n">
-        <v>3.275586179621268</v>
+        <v>3.275586179621267</v>
       </c>
       <c r="C1813" t="n">
         <v>3.128096071514691</v>
@@ -43232,7 +43232,7 @@
         <v>45276</v>
       </c>
       <c r="B1814" t="n">
-        <v>3.268822948291749</v>
+        <v>3.268822948291748</v>
       </c>
       <c r="C1814" t="n">
         <v>3.123696569025415</v>
@@ -43255,7 +43255,7 @@
         <v>45277</v>
       </c>
       <c r="B1815" t="n">
-        <v>3.249478190992881</v>
+        <v>3.24947819099288</v>
       </c>
       <c r="C1815" t="n">
         <v>3.109676345532145</v>
@@ -43278,7 +43278,7 @@
         <v>45278</v>
       </c>
       <c r="B1816" t="n">
-        <v>3.291576855321624</v>
+        <v>3.291576855321623</v>
       </c>
       <c r="C1816" t="n">
         <v>3.127125924287274</v>
@@ -43301,7 +43301,7 @@
         <v>45279</v>
       </c>
       <c r="B1817" t="n">
-        <v>3.289048749923557</v>
+        <v>3.289048749923556</v>
       </c>
       <c r="C1817" t="n">
         <v>3.126153974671351</v>
@@ -43324,7 +43324,7 @@
         <v>45280</v>
       </c>
       <c r="B1818" t="n">
-        <v>3.308072195160701</v>
+        <v>3.3080721951607</v>
       </c>
       <c r="C1818" t="n">
         <v>3.115456695754193</v>
@@ -43347,7 +43347,7 @@
         <v>45281</v>
       </c>
       <c r="B1819" t="n">
-        <v>3.318993081823467</v>
+        <v>3.318993081823466</v>
       </c>
       <c r="C1819" t="n">
         <v>3.125373651216407</v>
@@ -43370,7 +43370,7 @@
         <v>45282</v>
       </c>
       <c r="B1820" t="n">
-        <v>3.305392684942105</v>
+        <v>3.305392684942104</v>
       </c>
       <c r="C1820" t="n">
         <v>3.132226628875955</v>
@@ -43393,7 +43393,7 @@
         <v>45283</v>
       </c>
       <c r="B1821" t="n">
-        <v>3.312076663414905</v>
+        <v>3.312076663414904</v>
       </c>
       <c r="C1821" t="n">
         <v>3.134450814492048</v>
@@ -43416,22 +43416,22 @@
         <v>45284</v>
       </c>
       <c r="B1822" t="n">
-        <v>3.13782542222902</v>
+        <v>3.137825422229019</v>
       </c>
       <c r="C1822" t="n">
         <v>3.121045839271831</v>
       </c>
       <c r="D1822" t="n">
-        <v>0.2289977457812463</v>
+        <v>0.1457501494386354</v>
       </c>
       <c r="E1822" t="n">
-        <v>3.212288513270583</v>
+        <v>3.178989474733539</v>
       </c>
       <c r="F1822" t="n">
-        <v>1.791455612359032</v>
+        <v>1.710089642657863</v>
       </c>
       <c r="G1822" t="n">
-        <v>4.195919206687252</v>
+        <v>4.14709962486655</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231225.xlsx
+++ b/tame_output/ON/bt/strategyON_20231225.xlsx
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844647</v>
+        <v>3.118866618844648</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.123416866373823</v>
+        <v>3.123416866373824</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502551</v>
+        <v>3.141819250502552</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487812</v>
+        <v>3.146053372487813</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823383</v>
+        <v>3.146265744823384</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524823</v>
+        <v>3.157777201524824</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068703</v>
+        <v>3.157294380068704</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714845</v>
+        <v>3.147014107714846</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097101</v>
+        <v>3.163432091097102</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762261</v>
+        <v>3.169279212762262</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963479</v>
+        <v>3.18551435596348</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583694</v>
+        <v>3.199276732583695</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742724</v>
+        <v>3.238767863742725</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589524</v>
+        <v>3.260068416589525</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872957</v>
+        <v>3.306739876872958</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946329</v>
+        <v>3.31216459594633</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43048,7 +43048,7 @@
         <v>45268</v>
       </c>
       <c r="B1806" t="n">
-        <v>3.318449829143339</v>
+        <v>3.31844982914334</v>
       </c>
       <c r="C1806" t="n">
         <v>3.100133560631823</v>
@@ -43071,7 +43071,7 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308503</v>
+        <v>3.311781349308504</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
@@ -43094,7 +43094,7 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257516</v>
+        <v>3.271427670257517</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
@@ -43117,7 +43117,7 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.25296238744154</v>
+        <v>3.252962387441541</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
@@ -43140,7 +43140,7 @@
         <v>45272</v>
       </c>
       <c r="B1810" t="n">
-        <v>3.241257540662168</v>
+        <v>3.241257540662169</v>
       </c>
       <c r="C1810" t="n">
         <v>3.119070330776787</v>
@@ -43163,7 +43163,7 @@
         <v>45273</v>
       </c>
       <c r="B1811" t="n">
-        <v>3.285495323543324</v>
+        <v>3.285495323543325</v>
       </c>
       <c r="C1811" t="n">
         <v>3.132597942828719</v>
@@ -43186,7 +43186,7 @@
         <v>45274</v>
       </c>
       <c r="B1812" t="n">
-        <v>3.287726162978608</v>
+        <v>3.287726162978609</v>
       </c>
       <c r="C1812" t="n">
         <v>3.139185323079984</v>
@@ -43209,7 +43209,7 @@
         <v>45275</v>
       </c>
       <c r="B1813" t="n">
-        <v>3.275586179621267</v>
+        <v>3.275586179621268</v>
       </c>
       <c r="C1813" t="n">
         <v>3.128096071514691</v>
@@ -43232,7 +43232,7 @@
         <v>45276</v>
       </c>
       <c r="B1814" t="n">
-        <v>3.268822948291748</v>
+        <v>3.268822948291749</v>
       </c>
       <c r="C1814" t="n">
         <v>3.123696569025415</v>
@@ -43255,7 +43255,7 @@
         <v>45277</v>
       </c>
       <c r="B1815" t="n">
-        <v>3.24947819099288</v>
+        <v>3.249478190992881</v>
       </c>
       <c r="C1815" t="n">
         <v>3.109676345532145</v>
@@ -43278,7 +43278,7 @@
         <v>45278</v>
       </c>
       <c r="B1816" t="n">
-        <v>3.291576855321623</v>
+        <v>3.291576855321624</v>
       </c>
       <c r="C1816" t="n">
         <v>3.127125924287274</v>
@@ -43301,7 +43301,7 @@
         <v>45279</v>
       </c>
       <c r="B1817" t="n">
-        <v>3.289048749923556</v>
+        <v>3.289048749923557</v>
       </c>
       <c r="C1817" t="n">
         <v>3.126153974671351</v>
@@ -43324,7 +43324,7 @@
         <v>45280</v>
       </c>
       <c r="B1818" t="n">
-        <v>3.3080721951607</v>
+        <v>3.308072195160701</v>
       </c>
       <c r="C1818" t="n">
         <v>3.115456695754193</v>
@@ -43347,7 +43347,7 @@
         <v>45281</v>
       </c>
       <c r="B1819" t="n">
-        <v>3.318993081823466</v>
+        <v>3.318993081823467</v>
       </c>
       <c r="C1819" t="n">
         <v>3.125373651216407</v>
@@ -43370,7 +43370,7 @@
         <v>45282</v>
       </c>
       <c r="B1820" t="n">
-        <v>3.305392684942104</v>
+        <v>3.305392684942105</v>
       </c>
       <c r="C1820" t="n">
         <v>3.132226628875955</v>
@@ -43393,7 +43393,7 @@
         <v>45283</v>
       </c>
       <c r="B1821" t="n">
-        <v>3.312076663414904</v>
+        <v>3.312076663414905</v>
       </c>
       <c r="C1821" t="n">
         <v>3.134450814492048</v>
@@ -43416,7 +43416,7 @@
         <v>45284</v>
       </c>
       <c r="B1822" t="n">
-        <v>3.137825422229019</v>
+        <v>3.13782542222902</v>
       </c>
       <c r="C1822" t="n">
         <v>3.121045839271831</v>
